--- a/artfynd/A 8500-2022 artfynd.xlsx
+++ b/artfynd/A 8500-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8500-2022 artfynd.xlsx
+++ b/artfynd/A 8500-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,317 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120245573</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nyckelberget, Nyckelberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>674926</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6612969</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120245887</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>675032</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6613046</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120245686</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>674962</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6613044</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8500-2022 artfynd.xlsx
+++ b/artfynd/A 8500-2022 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120245573</v>
+        <v>120245686</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
+        <v>5169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,34 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nyckelberget, Nyckelberget, Upl</t>
+          <t>Nyhagen, Nyhagen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>674926</v>
+        <v>674962</v>
       </c>
       <c r="R3" t="n">
-        <v>6612969</v>
+        <v>6613044</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120245887</v>
+        <v>120245573</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,43 +910,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Upl</t>
+          <t>Nyckelberget, Nyckelberget, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>675032</v>
+        <v>674926</v>
       </c>
       <c r="R4" t="n">
-        <v>6613046</v>
+        <v>6612969</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120245686</v>
+        <v>120245887</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,38 +1012,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nyhagen, Nyhagen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674962</v>
+        <v>675032</v>
       </c>
       <c r="R5" t="n">
-        <v>6613044</v>
+        <v>6613046</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 8500-2022 artfynd.xlsx
+++ b/artfynd/A 8500-2022 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120245686</v>
+        <v>120245887</v>
       </c>
       <c r="B3" t="n">
-        <v>5169</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +808,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nyhagen, Nyhagen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>674962</v>
+        <v>675032</v>
       </c>
       <c r="R3" t="n">
-        <v>6613044</v>
+        <v>6613046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120245573</v>
+        <v>120245686</v>
       </c>
       <c r="B4" t="n">
-        <v>90545</v>
+        <v>5169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,34 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nyckelberget, Nyckelberget, Upl</t>
+          <t>Nyhagen, Nyhagen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674926</v>
+        <v>674962</v>
       </c>
       <c r="R4" t="n">
-        <v>6612969</v>
+        <v>6613044</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120245887</v>
+        <v>120245573</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,43 +1017,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Upl</t>
+          <t>Nyckelberget, Nyckelberget, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675032</v>
+        <v>674926</v>
       </c>
       <c r="R5" t="n">
-        <v>6613046</v>
+        <v>6612969</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 8500-2022 artfynd.xlsx
+++ b/artfynd/A 8500-2022 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120245686</v>
+        <v>120245573</v>
       </c>
       <c r="B4" t="n">
-        <v>5169</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Upl</t>
+          <t>Nyckelberget, Nyckelberget, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674962</v>
+        <v>674926</v>
       </c>
       <c r="R4" t="n">
-        <v>6613044</v>
+        <v>6612969</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120245573</v>
+        <v>120245686</v>
       </c>
       <c r="B5" t="n">
-        <v>90545</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,34 +1021,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nyckelberget, Nyckelberget, Upl</t>
+          <t>Nyhagen, Nyhagen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674926</v>
+        <v>674962</v>
       </c>
       <c r="R5" t="n">
-        <v>6612969</v>
+        <v>6613044</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 8500-2022 artfynd.xlsx
+++ b/artfynd/A 8500-2022 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120245887</v>
+        <v>120245686</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>5169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,43 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nyhagen, Nyhagen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675032</v>
+        <v>674962</v>
       </c>
       <c r="R3" t="n">
-        <v>6613046</v>
+        <v>6613044</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120245573</v>
+        <v>120245887</v>
       </c>
       <c r="B4" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +910,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nyckelberget, Nyckelberget, Upl</t>
+          <t>Nyhagen, Nyhagen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674926</v>
+        <v>675032</v>
       </c>
       <c r="R4" t="n">
-        <v>6612969</v>
+        <v>6613046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120245686</v>
+        <v>120245573</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>90545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,34 +1021,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Upl</t>
+          <t>Nyckelberget, Nyckelberget, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674962</v>
+        <v>674926</v>
       </c>
       <c r="R5" t="n">
-        <v>6613044</v>
+        <v>6612969</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 8500-2022 artfynd.xlsx
+++ b/artfynd/A 8500-2022 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120245686</v>
+        <v>120245573</v>
       </c>
       <c r="B3" t="n">
-        <v>5169</v>
+        <v>90545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,34 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Upl</t>
+          <t>Nyckelberget, Nyckelberget, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>674962</v>
+        <v>674926</v>
       </c>
       <c r="R3" t="n">
-        <v>6613044</v>
+        <v>6612969</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120245887</v>
+        <v>120245686</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>5169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,43 +910,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nyhagen, Nyhagen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>675032</v>
+        <v>674962</v>
       </c>
       <c r="R4" t="n">
-        <v>6613046</v>
+        <v>6613044</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120245573</v>
+        <v>120245887</v>
       </c>
       <c r="B5" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,38 +1012,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nyckelberget, Nyckelberget, Upl</t>
+          <t>Nyhagen, Nyhagen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674926</v>
+        <v>675032</v>
       </c>
       <c r="R5" t="n">
-        <v>6612969</v>
+        <v>6613046</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 8500-2022 artfynd.xlsx
+++ b/artfynd/A 8500-2022 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120245573</v>
+        <v>120245887</v>
       </c>
       <c r="B3" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +808,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nyckelberget, Nyckelberget, Upl</t>
+          <t>Nyhagen, Nyhagen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>674926</v>
+        <v>675032</v>
       </c>
       <c r="R3" t="n">
-        <v>6612969</v>
+        <v>6613046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120245686</v>
+        <v>120245573</v>
       </c>
       <c r="B4" t="n">
-        <v>5169</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,34 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Upl</t>
+          <t>Nyckelberget, Nyckelberget, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674962</v>
+        <v>674926</v>
       </c>
       <c r="R4" t="n">
-        <v>6613044</v>
+        <v>6612969</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120245887</v>
+        <v>120245686</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,43 +1017,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nyhagen, Nyhagen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675032</v>
+        <v>674962</v>
       </c>
       <c r="R5" t="n">
-        <v>6613046</v>
+        <v>6613044</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 8500-2022 artfynd.xlsx
+++ b/artfynd/A 8500-2022 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120245887</v>
+        <v>120245573</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,43 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Upl</t>
+          <t>Nyckelberget, Nyckelberget, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675032</v>
+        <v>674926</v>
       </c>
       <c r="R3" t="n">
-        <v>6613046</v>
+        <v>6612969</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120245573</v>
+        <v>120245887</v>
       </c>
       <c r="B4" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +910,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nyckelberget, Nyckelberget, Upl</t>
+          <t>Nyhagen, Nyhagen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674926</v>
+        <v>675032</v>
       </c>
       <c r="R4" t="n">
-        <v>6612969</v>
+        <v>6613046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 8500-2022 artfynd.xlsx
+++ b/artfynd/A 8500-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>458777</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675039.7889244512</v>
+        <v>675040</v>
       </c>
       <c r="R2" t="n">
-        <v>6613009.613318151</v>
+        <v>6613010</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1998-04-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1998-04-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120245686</v>
+        <v>120245573</v>
       </c>
       <c r="B3" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,34 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Upl</t>
+          <t>Nyckelberget, Nyckelberget, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>674962</v>
+        <v>674926</v>
       </c>
       <c r="R3" t="n">
-        <v>6613044</v>
+        <v>6612969</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120245573</v>
+        <v>120245887</v>
       </c>
       <c r="B4" t="n">
-        <v>90595</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,34 +889,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nyckelberget, Nyckelberget, Upl</t>
+          <t>Nyhagen, Nyhagen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674926</v>
+        <v>675032</v>
       </c>
       <c r="R4" t="n">
-        <v>6612969</v>
+        <v>6613046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,55 +980,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120245887</v>
+        <v>120245686</v>
       </c>
       <c r="B5" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nyhagen, Nyhagen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675032</v>
+        <v>674962</v>
       </c>
       <c r="R5" t="n">
-        <v>6613046</v>
+        <v>6613044</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,6 +1074,237 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120245340</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>674884</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6613060</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120245372</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>674900</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6613084</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orkesta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Tre fröställningar</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
